--- a/DT_更新奖励数据表.xlsx
+++ b/DT_更新奖励数据表.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t xml:space="preserve">  </t>
   </si>
@@ -94,9 +94,6 @@
     <t xml:space="preserve">3</t>
   </si>
   <si>
-    <t xml:space="preserve">3000</t>
-  </si>
-  <si>
     <t xml:space="preserve">/Script/Engine.Texture2D'/Game/BreakTheBricks/Art/UI/主页/Texture/T_UI_Item_Gtid_金币_01a.T_UI_Item_Gtid_金币_01a'</t>
   </si>
   <si>
@@ -119,9 +116,6 @@
   </si>
   <si>
     <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1200</t>
   </si>
   <si>
     <t xml:space="preserve">/Script/Engine.Texture2D'/Game/BreakTheBricks/Art/UI/主页/Texture/T_UI_Item_Gtid_钻石_01b.T_UI_Item_Gtid_钻石_01b'</t>
@@ -194,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -209,6 +203,9 @@
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0">
       <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
+      <alignment vertical="bottom" wrapText="true"/>
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
@@ -592,32 +589,32 @@
       <c r="C2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="5">
+        <v>6000</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="6" t="s">
         <v>13</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="L2" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>21</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
@@ -633,37 +630,37 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="5">
+        <v>5000</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="H3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="5" t="s">
+      <c r="L3" s="6" t="s">
         <v>26</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>28</v>
       </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
